--- a/재고수불26.04.02.xlsx
+++ b/재고수불26.04.02.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1779</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1805</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9460" uniqueCount="1853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9605" uniqueCount="1882">
   <si>
     <t>LOT번호</t>
   </si>
@@ -6175,6 +6175,122 @@
   </si>
   <si>
     <t>1.8-2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순도문제로 55,000-&gt;50,000 하향판매함으로써 관리 용이하게 기존 4만립 제품에서 600g 제품으로 판매함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610090P2KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610090P3KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5-1.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.75-2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건조감량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N240470P5CN0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건조감량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정선감량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정선입고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정선입고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610080P2KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610080P3KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.6-1.85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.85-2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.26</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6306,7 +6422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6376,9 +6492,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -6659,7 +6772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1779"/>
+  <dimension ref="A1:N1805"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="5" customWidth="1"/>
@@ -47865,7 +47978,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="1201" spans="1:14" ht="30" customHeight="1">
+    <row r="1201" spans="1:12" ht="30" customHeight="1">
       <c r="A1201" s="3">
         <v>1200</v>
       </c>
@@ -47894,7 +48007,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="1202" spans="1:14" ht="30" customHeight="1">
+    <row r="1202" spans="1:12" ht="30" customHeight="1">
       <c r="A1202" s="3">
         <v>1201</v>
       </c>
@@ -47923,7 +48036,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="1203" spans="1:14" ht="30" customHeight="1">
+    <row r="1203" spans="1:12" ht="30" customHeight="1">
       <c r="A1203" s="3">
         <v>1202</v>
       </c>
@@ -47954,14 +48067,8 @@
       <c r="L1203" s="12">
         <v>5</v>
       </c>
-      <c r="M1203" s="2">
-        <v>97</v>
-      </c>
-      <c r="N1203" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="1204" spans="1:14" ht="30" customHeight="1">
+    </row>
+    <row r="1204" spans="1:12" ht="30" customHeight="1">
       <c r="A1204" s="3">
         <v>1203</v>
       </c>
@@ -47992,14 +48099,8 @@
       <c r="L1204" s="12">
         <v>6</v>
       </c>
-      <c r="M1204" s="2">
-        <v>98</v>
-      </c>
-      <c r="N1204" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="1205" spans="1:14" ht="30" customHeight="1">
+    </row>
+    <row r="1205" spans="1:12" ht="30" customHeight="1">
       <c r="A1205" s="3">
         <v>1204</v>
       </c>
@@ -48030,14 +48131,8 @@
       <c r="L1205" s="12">
         <v>7</v>
       </c>
-      <c r="M1205" s="2">
-        <v>98</v>
-      </c>
-      <c r="N1205" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="1206" spans="1:14" ht="30" customHeight="1">
+    </row>
+    <row r="1206" spans="1:12" ht="30" customHeight="1">
       <c r="A1206" s="3">
         <v>1205</v>
       </c>
@@ -48066,7 +48161,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="1207" spans="1:14" ht="30" customHeight="1">
+    <row r="1207" spans="1:12" ht="30" customHeight="1">
       <c r="A1207" s="3">
         <v>1206</v>
       </c>
@@ -48095,7 +48190,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="1208" spans="1:14" ht="30" customHeight="1">
+    <row r="1208" spans="1:12" ht="30" customHeight="1">
       <c r="A1208" s="3">
         <v>1207</v>
       </c>
@@ -48124,7 +48219,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="1209" spans="1:14" ht="30" customHeight="1">
+    <row r="1209" spans="1:12" ht="30" customHeight="1">
       <c r="A1209" s="3">
         <v>1208</v>
       </c>
@@ -48153,7 +48248,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="1210" spans="1:14" ht="30" customHeight="1">
+    <row r="1210" spans="1:12" ht="30" customHeight="1">
       <c r="A1210" s="3">
         <v>1209</v>
       </c>
@@ -48182,7 +48277,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="1211" spans="1:14" ht="30" customHeight="1">
+    <row r="1211" spans="1:12" ht="30" customHeight="1">
       <c r="A1211" s="3">
         <v>1210</v>
       </c>
@@ -48210,8 +48305,11 @@
       <c r="I1211" s="20">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="1212" spans="1:14" ht="30" customHeight="1">
+      <c r="L1211" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:12" ht="30" customHeight="1">
       <c r="A1212" s="3">
         <v>1211</v>
       </c>
@@ -48239,8 +48337,11 @@
       <c r="I1212" s="20">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="1213" spans="1:14" ht="30" customHeight="1">
+      <c r="L1212" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:12" ht="30" customHeight="1">
       <c r="A1213" s="3">
         <v>1212</v>
       </c>
@@ -48268,8 +48369,11 @@
       <c r="I1213" s="20">
         <v>1.7</v>
       </c>
-    </row>
-    <row r="1214" spans="1:14" ht="30" customHeight="1">
+      <c r="L1213" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:12" ht="30" customHeight="1">
       <c r="A1214" s="3">
         <v>1213</v>
       </c>
@@ -48301,7 +48405,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1215" spans="1:14" ht="30" customHeight="1">
+    <row r="1215" spans="1:12" ht="30" customHeight="1">
       <c r="A1215" s="3">
         <v>1214</v>
       </c>
@@ -48333,7 +48437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1216" spans="1:14" ht="30" customHeight="1">
+    <row r="1216" spans="1:12" ht="30" customHeight="1">
       <c r="A1216" s="3">
         <v>1215</v>
       </c>
@@ -52487,7 +52591,7 @@
         <v>46069</v>
       </c>
       <c r="L1341" s="12">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1342" spans="1:14" ht="30" customHeight="1">
@@ -66990,7 +67094,7 @@
     </row>
     <row r="1764" spans="1:14" ht="30" customHeight="1">
       <c r="A1764" s="3">
-        <v>1766</v>
+        <v>1763</v>
       </c>
       <c r="B1764" s="5" t="s">
         <v>1839</v>
@@ -67022,7 +67126,7 @@
     </row>
     <row r="1765" spans="1:14" ht="30" customHeight="1">
       <c r="A1765" s="3">
-        <v>1767</v>
+        <v>1764</v>
       </c>
       <c r="B1765" s="5" t="s">
         <v>1839</v>
@@ -67054,7 +67158,7 @@
     </row>
     <row r="1766" spans="1:14" ht="30" customHeight="1">
       <c r="A1766" s="3">
-        <v>1768</v>
+        <v>1765</v>
       </c>
       <c r="B1766" s="5" t="s">
         <v>1839</v>
@@ -67086,7 +67190,7 @@
     </row>
     <row r="1767" spans="1:14" ht="30" customHeight="1">
       <c r="A1767" s="3">
-        <v>1769</v>
+        <v>1766</v>
       </c>
       <c r="B1767" s="5" t="s">
         <v>1839</v>
@@ -67118,7 +67222,7 @@
     </row>
     <row r="1768" spans="1:14" ht="30" customHeight="1">
       <c r="A1768" s="3">
-        <v>1770</v>
+        <v>1767</v>
       </c>
       <c r="B1768" s="5" t="s">
         <v>1839</v>
@@ -67150,7 +67254,7 @@
     </row>
     <row r="1769" spans="1:14" ht="30" customHeight="1">
       <c r="A1769" s="3">
-        <v>1771</v>
+        <v>1768</v>
       </c>
       <c r="B1769" s="5" t="s">
         <v>1839</v>
@@ -67182,7 +67286,7 @@
     </row>
     <row r="1770" spans="1:14" ht="30" customHeight="1">
       <c r="A1770" s="3">
-        <v>1772</v>
+        <v>1769</v>
       </c>
       <c r="B1770" s="5" t="s">
         <v>1839</v>
@@ -67214,7 +67318,7 @@
     </row>
     <row r="1771" spans="1:14" ht="30" customHeight="1">
       <c r="A1771" s="3">
-        <v>1773</v>
+        <v>1770</v>
       </c>
       <c r="B1771" s="5" t="s">
         <v>1839</v>
@@ -67246,7 +67350,7 @@
     </row>
     <row r="1772" spans="1:14" ht="30" customHeight="1">
       <c r="A1772" s="3">
-        <v>1774</v>
+        <v>1771</v>
       </c>
       <c r="B1772" s="5" t="s">
         <v>1839</v>
@@ -67278,7 +67382,7 @@
     </row>
     <row r="1773" spans="1:14" ht="30" customHeight="1">
       <c r="A1773" s="3">
-        <v>1775</v>
+        <v>1772</v>
       </c>
       <c r="B1773" s="5" t="s">
         <v>1839</v>
@@ -67309,8 +67413,8 @@
       </c>
     </row>
     <row r="1774" spans="1:14" ht="30" customHeight="1">
-      <c r="A1774" s="25">
-        <v>1776</v>
+      <c r="A1774" s="3">
+        <v>1773</v>
       </c>
       <c r="B1774" s="5" t="s">
         <v>1839</v>
@@ -67348,7 +67452,7 @@
     </row>
     <row r="1775" spans="1:14" ht="30" customHeight="1">
       <c r="A1775" s="3">
-        <v>1777</v>
+        <v>1774</v>
       </c>
       <c r="B1775" s="5" t="s">
         <v>1839</v>
@@ -67380,7 +67484,7 @@
     </row>
     <row r="1776" spans="1:14" ht="30" customHeight="1">
       <c r="A1776" s="3">
-        <v>1778</v>
+        <v>1775</v>
       </c>
       <c r="B1776" s="5" t="s">
         <v>1839</v>
@@ -67410,9 +67514,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1777" spans="1:12" ht="30" customHeight="1">
+    <row r="1777" spans="1:14" ht="30" customHeight="1">
       <c r="A1777" s="3">
-        <v>1779</v>
+        <v>1776</v>
       </c>
       <c r="B1777" s="5" t="s">
         <v>1839</v>
@@ -67442,9 +67546,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1778" spans="1:12" ht="30" customHeight="1">
+    <row r="1778" spans="1:14" ht="30" customHeight="1">
       <c r="A1778" s="3">
-        <v>1780</v>
+        <v>1777</v>
       </c>
       <c r="B1778" s="5" t="s">
         <v>1839</v>
@@ -67474,9 +67578,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1779" spans="1:12" ht="30" customHeight="1">
+    <row r="1779" spans="1:14" ht="30" customHeight="1">
       <c r="A1779" s="3">
-        <v>1781</v>
+        <v>1778</v>
       </c>
       <c r="B1779" s="5" t="s">
         <v>1839</v>
@@ -67506,8 +67610,909 @@
         <v>5</v>
       </c>
     </row>
+    <row r="1780" spans="1:14" ht="30" customHeight="1">
+      <c r="A1780" s="3">
+        <v>1779</v>
+      </c>
+      <c r="B1780" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C1780" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="D1780" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1780" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="F1780" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1780" s="18"/>
+      <c r="H1780" s="15">
+        <v>12.9</v>
+      </c>
+      <c r="I1780" s="15">
+        <v>91</v>
+      </c>
+      <c r="J1780" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K1780" s="8" t="s">
+        <v>1854</v>
+      </c>
+      <c r="L1780" s="12">
+        <v>10</v>
+      </c>
+      <c r="M1780" s="2">
+        <v>98</v>
+      </c>
+      <c r="N1780" s="2">
+        <v>88.8</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:14" ht="30" customHeight="1">
+      <c r="A1781" s="3">
+        <v>1780</v>
+      </c>
+      <c r="B1781" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C1781" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1781" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1781" s="9" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F1781" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1781" s="20">
+        <v>9.4</v>
+      </c>
+      <c r="I1781" s="20">
+        <v>3</v>
+      </c>
+      <c r="J1781" s="5" t="s">
+        <v>1855</v>
+      </c>
+      <c r="L1781" s="12">
+        <v>5</v>
+      </c>
+      <c r="M1781" s="2">
+        <v>97</v>
+      </c>
+      <c r="N1781" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:14" ht="30" customHeight="1">
+      <c r="A1782" s="3">
+        <v>1781</v>
+      </c>
+      <c r="B1782" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C1782" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1782" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1782" s="9" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F1782" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1782" s="20">
+        <v>11.1</v>
+      </c>
+      <c r="I1782" s="20">
+        <v>0</v>
+      </c>
+      <c r="J1782" s="5" t="s">
+        <v>1855</v>
+      </c>
+      <c r="L1782" s="12">
+        <v>6</v>
+      </c>
+      <c r="M1782" s="2">
+        <v>98</v>
+      </c>
+      <c r="N1782" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:14" ht="30" customHeight="1">
+      <c r="A1783" s="3">
+        <v>1782</v>
+      </c>
+      <c r="B1783" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C1783" s="8" t="s">
+        <v>903</v>
+      </c>
+      <c r="D1783" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1783" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="F1783" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1783" s="18"/>
+      <c r="H1783" s="15">
+        <v>160</v>
+      </c>
+      <c r="I1783" s="15">
+        <v>0</v>
+      </c>
+      <c r="J1783" s="3"/>
+      <c r="K1783" s="8"/>
+      <c r="L1783" s="12">
+        <v>1</v>
+      </c>
+      <c r="M1783" s="2">
+        <v>90.5</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:14" ht="30" customHeight="1">
+      <c r="A1784" s="3">
+        <v>1783</v>
+      </c>
+      <c r="B1784" s="5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C1784" s="9" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D1784" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1784" s="9" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F1784" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1784" s="20">
+        <v>1.3</v>
+      </c>
+      <c r="I1784" s="20">
+        <v>152.19999999999999</v>
+      </c>
+      <c r="K1784" s="9">
+        <v>46131</v>
+      </c>
+      <c r="L1784" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:14" ht="30" customHeight="1">
+      <c r="A1785" s="3">
+        <v>1784</v>
+      </c>
+      <c r="B1785" s="5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C1785" s="9" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D1785" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1785" s="9" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F1785" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1785" s="20">
+        <v>8.9</v>
+      </c>
+      <c r="I1785" s="20">
+        <v>143.30000000000001</v>
+      </c>
+      <c r="K1785" s="9">
+        <v>46131</v>
+      </c>
+      <c r="L1785" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:14" ht="30" customHeight="1">
+      <c r="A1786" s="3">
+        <v>1785</v>
+      </c>
+      <c r="B1786" s="5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C1786" s="9" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D1786" s="5" t="s">
+        <v>1856</v>
+      </c>
+      <c r="E1786" s="9" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F1786" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1786" s="20">
+        <v>143.30000000000001</v>
+      </c>
+      <c r="I1786" s="20">
+        <v>0</v>
+      </c>
+      <c r="K1786" s="9">
+        <v>46131</v>
+      </c>
+      <c r="L1786" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:14" ht="30" customHeight="1">
+      <c r="A1787" s="3">
+        <v>1786</v>
+      </c>
+      <c r="B1787" s="5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C1787" s="9" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D1787" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1787" s="9" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F1787" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1787" s="19">
+        <v>109.7</v>
+      </c>
+      <c r="I1787" s="20">
+        <v>109.7</v>
+      </c>
+      <c r="K1787" s="9" t="s">
+        <v>1859</v>
+      </c>
+      <c r="L1787" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:14" ht="30" customHeight="1">
+      <c r="A1788" s="3">
+        <v>1787</v>
+      </c>
+      <c r="B1788" s="5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C1788" s="9" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D1788" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1788" s="9" t="s">
+        <v>1858</v>
+      </c>
+      <c r="F1788" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1788" s="19">
+        <v>33.6</v>
+      </c>
+      <c r="I1788" s="20">
+        <v>33.6</v>
+      </c>
+      <c r="K1788" s="9" t="s">
+        <v>1860</v>
+      </c>
+      <c r="L1788" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:14" ht="30" customHeight="1">
+      <c r="A1789" s="3">
+        <v>1788</v>
+      </c>
+      <c r="B1789" s="5" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C1789" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1789" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1789" s="9" t="s">
+        <v>1812</v>
+      </c>
+      <c r="F1789" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1789" s="20">
+        <v>0.62</v>
+      </c>
+      <c r="I1789" s="20">
+        <v>28.19</v>
+      </c>
+      <c r="L1789" s="12">
+        <v>11</v>
+      </c>
+      <c r="M1789" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:14" ht="30" customHeight="1">
+      <c r="A1790" s="3">
+        <v>1789</v>
+      </c>
+      <c r="B1790" s="5" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C1790" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="D1790" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1790" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="F1790" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1790" s="20">
+        <v>700</v>
+      </c>
+      <c r="I1790" s="20">
+        <v>3500</v>
+      </c>
+      <c r="J1790" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L1790" s="12">
+        <v>2</v>
+      </c>
+      <c r="M1790" s="2">
+        <v>99</v>
+      </c>
+      <c r="N1790" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:14" ht="30" customHeight="1">
+      <c r="A1791" s="3">
+        <v>1790</v>
+      </c>
+      <c r="B1791" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1791" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1791" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1791" s="9" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F1791" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1791" s="20">
+        <v>1.8</v>
+      </c>
+      <c r="I1791" s="20">
+        <v>0</v>
+      </c>
+      <c r="J1791" s="5" t="s">
+        <v>1864</v>
+      </c>
+      <c r="L1791" s="12">
+        <v>4</v>
+      </c>
+      <c r="M1791" s="2">
+        <v>99.5</v>
+      </c>
+      <c r="N1791" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:14" ht="30" customHeight="1">
+      <c r="A1792" s="3">
+        <v>1791</v>
+      </c>
+      <c r="B1792" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1792" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1792" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1792" s="9" t="s">
+        <v>1698</v>
+      </c>
+      <c r="F1792" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1792" s="20">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="I1792" s="20">
+        <v>0</v>
+      </c>
+      <c r="J1792" s="5" t="s">
+        <v>1864</v>
+      </c>
+      <c r="L1792" s="12">
+        <v>5</v>
+      </c>
+      <c r="M1792" s="2">
+        <v>99</v>
+      </c>
+      <c r="N1792" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:14" ht="30" customHeight="1">
+      <c r="A1793" s="3">
+        <v>1792</v>
+      </c>
+      <c r="B1793" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1793" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1793" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1793" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1793" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1793" s="20">
+        <v>11.71</v>
+      </c>
+      <c r="I1793" s="20">
+        <v>0</v>
+      </c>
+      <c r="J1793" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K1793" s="8"/>
+      <c r="L1793" s="12">
+        <v>1</v>
+      </c>
+      <c r="M1793" s="2">
+        <v>97</v>
+      </c>
+      <c r="N1793" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:14" ht="30" customHeight="1">
+      <c r="A1794" s="3">
+        <v>1793</v>
+      </c>
+      <c r="B1794" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C1794" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1794" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1794" s="9" t="s">
+        <v>1652</v>
+      </c>
+      <c r="F1794" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1794" s="20">
+        <v>2.8</v>
+      </c>
+      <c r="I1794" s="20">
+        <v>0</v>
+      </c>
+      <c r="J1794" s="5" t="s">
+        <v>1866</v>
+      </c>
+      <c r="L1794" s="12">
+        <v>12</v>
+      </c>
+      <c r="M1794" s="2">
+        <v>97.5</v>
+      </c>
+      <c r="N1794" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:14" ht="30" customHeight="1">
+      <c r="A1795" s="3">
+        <v>1794</v>
+      </c>
+      <c r="B1795" s="5" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C1795" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1795" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1795" s="8" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F1795" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1795" s="18"/>
+      <c r="H1795" s="15">
+        <v>44</v>
+      </c>
+      <c r="I1795" s="15">
+        <v>96.2</v>
+      </c>
+      <c r="J1795" s="3"/>
+      <c r="K1795" s="8"/>
+      <c r="L1795" s="12">
+        <v>1</v>
+      </c>
+      <c r="M1795" s="2">
+        <v>98</v>
+      </c>
+      <c r="N1795" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:14" ht="30" customHeight="1">
+      <c r="A1796" s="3">
+        <v>1795</v>
+      </c>
+      <c r="B1796" s="5" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C1796" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1796" s="3" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E1796" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1796" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1796" s="20">
+        <v>1</v>
+      </c>
+      <c r="I1796" s="20">
+        <v>95.2</v>
+      </c>
+      <c r="L1796" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:14" ht="30" customHeight="1">
+      <c r="A1797" s="3">
+        <v>1796</v>
+      </c>
+      <c r="B1797" s="5" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C1797" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="D1797" s="5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E1797" s="9" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F1797" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1797" s="20">
+        <v>6.72</v>
+      </c>
+      <c r="I1797" s="20">
+        <v>115.68</v>
+      </c>
+      <c r="K1797" s="9">
+        <v>46132</v>
+      </c>
+      <c r="L1797" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:14" ht="30" customHeight="1">
+      <c r="A1798" s="3">
+        <v>1797</v>
+      </c>
+      <c r="B1798" s="5" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C1798" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="D1798" s="5" t="s">
+        <v>1870</v>
+      </c>
+      <c r="E1798" s="9" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F1798" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1798" s="20">
+        <v>12.28</v>
+      </c>
+      <c r="I1798" s="20">
+        <v>103.4</v>
+      </c>
+      <c r="K1798" s="9">
+        <v>46132</v>
+      </c>
+      <c r="L1798" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:14" ht="30" customHeight="1">
+      <c r="A1799" s="3">
+        <v>1798</v>
+      </c>
+      <c r="B1799" s="5" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C1799" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="D1799" s="5" t="s">
+        <v>1871</v>
+      </c>
+      <c r="E1799" s="9" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F1799" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1799" s="20">
+        <v>103.4</v>
+      </c>
+      <c r="I1799" s="20">
+        <v>0</v>
+      </c>
+      <c r="K1799" s="9">
+        <v>46132</v>
+      </c>
+      <c r="L1799" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:14" ht="30" customHeight="1">
+      <c r="A1800" s="3">
+        <v>1799</v>
+      </c>
+      <c r="B1800" s="5" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C1800" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="D1800" s="5" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E1800" s="9" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F1800" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1800" s="19">
+        <v>34.9</v>
+      </c>
+      <c r="I1800" s="20">
+        <v>34.9</v>
+      </c>
+      <c r="K1800" s="9" t="s">
+        <v>1876</v>
+      </c>
+      <c r="L1800" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:14" ht="30" customHeight="1">
+      <c r="A1801" s="3">
+        <v>1800</v>
+      </c>
+      <c r="B1801" s="5" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C1801" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="D1801" s="5" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E1801" s="9" t="s">
+        <v>1875</v>
+      </c>
+      <c r="F1801" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1801" s="19">
+        <v>68.5</v>
+      </c>
+      <c r="I1801" s="20">
+        <v>68.5</v>
+      </c>
+      <c r="K1801" s="9" t="s">
+        <v>1877</v>
+      </c>
+      <c r="L1801" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:14" ht="30" customHeight="1">
+      <c r="A1802" s="3">
+        <v>1801</v>
+      </c>
+      <c r="B1802" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C1802" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="D1802" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1802" s="9" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F1802" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1802" s="20">
+        <v>1.24</v>
+      </c>
+      <c r="I1802" s="20">
+        <v>18.760000000000002</v>
+      </c>
+      <c r="L1802" s="12">
+        <v>3</v>
+      </c>
+      <c r="M1802" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:14" ht="30" customHeight="1">
+      <c r="A1803" s="3">
+        <v>1802</v>
+      </c>
+      <c r="B1803" s="5" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C1803" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1803" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1803" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F1803" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1803" s="18"/>
+      <c r="H1803" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I1803" s="15">
+        <v>23.6</v>
+      </c>
+      <c r="J1803" s="3"/>
+      <c r="K1803" s="8"/>
+      <c r="L1803" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:14" ht="30" customHeight="1">
+      <c r="A1804" s="3">
+        <v>1803</v>
+      </c>
+      <c r="B1804" s="5" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C1804" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1804" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1804" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F1804" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1804" s="18"/>
+      <c r="H1804" s="15">
+        <v>15.7</v>
+      </c>
+      <c r="I1804" s="15">
+        <v>7.9</v>
+      </c>
+      <c r="J1804" s="3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="K1804" s="8"/>
+      <c r="L1804" s="12">
+        <v>5</v>
+      </c>
+      <c r="M1804" s="2">
+        <v>91.5</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:14" ht="30" customHeight="1">
+      <c r="A1805" s="3">
+        <v>1804</v>
+      </c>
+      <c r="B1805" s="5" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C1805" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D1805" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1805" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F1805" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1805" s="18"/>
+      <c r="H1805" s="15">
+        <v>5</v>
+      </c>
+      <c r="I1805" s="15">
+        <v>0</v>
+      </c>
+      <c r="J1805" s="3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="K1805" s="8"/>
+      <c r="L1805" s="12">
+        <v>6</v>
+      </c>
+      <c r="M1805" s="2">
+        <v>91.5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1779"/>
+  <autoFilter ref="A1:L1805"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/재고수불26.04.02.xlsx
+++ b/재고수불26.04.02.xlsx
@@ -74386,10 +74386,10 @@
       <c r="F1945" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1945" s="18">
+      <c r="G1945" s="18"/>
+      <c r="H1945" s="15">
         <v>4.3099999999999996</v>
       </c>
-      <c r="H1945" s="15"/>
       <c r="I1945" s="15">
         <v>841</v>
       </c>
